--- a/data/satisfaction_detail/2026/1-8月/商务简餐.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/商务简餐.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.5</v>
+        <v>9.578068332537534</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>9.861299273170991</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.83</v>
+        <v>9.828285320176137</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.881870656268237</v>
       </c>
     </row>
     <row r="4">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.860610642474402</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.857832776274602</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.74</v>
+        <v>9.743193272852672</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.82</v>
+        <v>9.817763807098519</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.884876120749112</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.92</v>
+        <v>9.908330415406652</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.882833572072789</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.9</v>
+        <v>9.899996816807258</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.92</v>
+        <v>9.923608679505545</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.91</v>
+        <v>9.904163616106956</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.60396625815693</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.881841477001432</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.894890445116452</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.91</v>
+        <v>9.904163616106956</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9.050000000000001</v>
+        <v>9.252507294816702</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.779778237572286</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>8.34</v>
+        <v>8.65265785503915</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.33</v>
+        <v>9.742356152575246</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.57</v>
+        <v>9.587116027375457</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.766163191681256</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.23</v>
+        <v>9.263223513183723</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.81</v>
+        <v>9.786512812350788</v>
       </c>
     </row>
     <row r="15">
